--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Credit Risk Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Credit Risk Fund.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\OPERAT\Factsheet 2013-14\January 2025\ISIN Port 310125_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\OPERAT\Factsheet 2013-14\May 2025\ISIN Portfolios 310525\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="219">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -27,7 +27,7 @@
     <t>ICICI Prudential Credit Risk Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -75,19 +75,31 @@
     <t>SOV</t>
   </si>
   <si>
-    <t>IN0020230036</t>
-  </si>
-  <si>
-    <t>IN0020230085</t>
-  </si>
-  <si>
     <t>IN0020240126</t>
   </si>
   <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
     <t>State Government of Karnataka</t>
   </si>
   <si>
-    <t>IN1920140093</t>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds</t>
@@ -99,460 +111,436 @@
     <t>INE665L07040</t>
   </si>
   <si>
+    <t>FITCH AA</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd. **</t>
+  </si>
+  <si>
+    <t>INE205A08038</t>
+  </si>
+  <si>
+    <t>ICRA AA</t>
+  </si>
+  <si>
+    <t>Bamboo Hotels &amp; Global Centre (Delhi) Pvt Ltd. **</t>
+  </si>
+  <si>
+    <t>INE755L07015</t>
+  </si>
+  <si>
+    <t>ICRA A+(CE)</t>
+  </si>
+  <si>
+    <t>Aadhar Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE883F07314</t>
+  </si>
+  <si>
+    <t>Nirma Ltd. **</t>
+  </si>
+  <si>
+    <t>INE091A07208</t>
+  </si>
+  <si>
+    <t>CRISIL AA</t>
+  </si>
+  <si>
+    <t>DLF Home Developers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE351E07018</t>
+  </si>
+  <si>
+    <t>SIS Ltd. **</t>
+  </si>
+  <si>
+    <t>INE285J07058</t>
+  </si>
+  <si>
+    <t>CRISIL AA-</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd **</t>
+  </si>
+  <si>
+    <t>INE220B08142</t>
+  </si>
+  <si>
+    <t>JM Financial Home Loans **</t>
+  </si>
+  <si>
+    <t>INE01A207146</t>
+  </si>
+  <si>
+    <t>TVS Credit Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE729N08055</t>
+  </si>
+  <si>
+    <t>CRISIL AA+</t>
+  </si>
+  <si>
+    <t>Indostar Capital Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE896L07AJ8</t>
+  </si>
+  <si>
+    <t>CARE AA-</t>
+  </si>
+  <si>
+    <t>INE729N08071</t>
+  </si>
+  <si>
+    <t>Kogta Financial (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE192U07350</t>
+  </si>
+  <si>
+    <t>CARE A+</t>
+  </si>
+  <si>
+    <t>INE192U07343</t>
+  </si>
+  <si>
+    <t>ICRA A+</t>
+  </si>
+  <si>
+    <t>Ashiana Housing Ltd. **</t>
+  </si>
+  <si>
+    <t>INE365D07085</t>
+  </si>
+  <si>
+    <t>CARE A</t>
+  </si>
+  <si>
+    <t>Aadharshila Infratech Pvt Ltd **</t>
+  </si>
+  <si>
+    <t>INE0REQ08017</t>
+  </si>
+  <si>
+    <t>CARE AA+</t>
+  </si>
+  <si>
+    <t>JM Financial Asset Recosntruction Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE265J07514</t>
+  </si>
+  <si>
+    <t>ICRA AA-</t>
+  </si>
+  <si>
+    <t>State Bank of India ( Tier II Bond under Basel III ) **</t>
+  </si>
+  <si>
+    <t>INE062A08256</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
+    <t>Prism Johnson Ltd. **</t>
+  </si>
+  <si>
+    <t>INE010A08156</t>
+  </si>
+  <si>
+    <t>FITCH A+</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE233A08071</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd. **</t>
+  </si>
+  <si>
+    <t>INE775A08089</t>
+  </si>
+  <si>
+    <t>FITCH AAA</t>
+  </si>
+  <si>
+    <t>INE010A08149</t>
+  </si>
+  <si>
+    <t>Macrotech Developers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE670K07257</t>
+  </si>
+  <si>
+    <t>Eris Lifesciences Ltd. **</t>
+  </si>
+  <si>
+    <t>INE406M08029</t>
+  </si>
+  <si>
+    <t>INE406M08011</t>
+  </si>
+  <si>
+    <t>Ess Kay Fincorp Ltd **</t>
+  </si>
+  <si>
+    <t>INE124N07689</t>
+  </si>
+  <si>
+    <t>Aptus Value Housing Finance India Ltd. **</t>
+  </si>
+  <si>
+    <t>INE852O07147</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd. **</t>
+  </si>
+  <si>
+    <t>INE093I07082</t>
+  </si>
+  <si>
+    <t>Creamline Dairy Products Ltd **</t>
+  </si>
+  <si>
+    <t>INE412L08029</t>
+  </si>
+  <si>
     <t>FITCH AA-</t>
   </si>
   <si>
-    <t>Bamboo Hotels &amp; Global Centre (Delhi) Pvt Ltd. **</t>
-  </si>
-  <si>
-    <t>INE755L07015</t>
-  </si>
-  <si>
-    <t>ICRA A+(CE)</t>
-  </si>
-  <si>
-    <t>Aadhar Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE883F07314</t>
-  </si>
-  <si>
-    <t>ICRA AA</t>
-  </si>
-  <si>
-    <t>Nirma Ltd. **</t>
-  </si>
-  <si>
-    <t>INE091A07208</t>
-  </si>
-  <si>
-    <t>CRISIL AA</t>
-  </si>
-  <si>
-    <t>DLF Home Developers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE351E07018</t>
-  </si>
-  <si>
-    <t>JM Financial Home Loans **</t>
-  </si>
-  <si>
-    <t>INE01A207146</t>
-  </si>
-  <si>
-    <t>TVS Credit Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE729N08055</t>
-  </si>
-  <si>
-    <t>Kalpataru Projects International Ltd **</t>
-  </si>
-  <si>
-    <t>INE220B08142</t>
-  </si>
-  <si>
-    <t>FITCH AA</t>
-  </si>
-  <si>
-    <t>INE729N08071</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE658R08180</t>
-  </si>
-  <si>
-    <t>Macrotech Developers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE670K07257</t>
-  </si>
-  <si>
-    <t>ICRA AA-</t>
-  </si>
-  <si>
-    <t>Kogta Financial (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE192U07343</t>
-  </si>
-  <si>
-    <t>ICRA A+</t>
-  </si>
-  <si>
-    <t>Aadharshila Infratech Pvt Ltd **</t>
-  </si>
-  <si>
-    <t>INE0REQ08017</t>
-  </si>
-  <si>
-    <t>CARE AA+</t>
-  </si>
-  <si>
-    <t>Ashiana Housing Ltd. **</t>
-  </si>
-  <si>
-    <t>INE365D07085</t>
-  </si>
-  <si>
-    <t>CARE A</t>
+    <t>INE670K07273</t>
+  </si>
+  <si>
+    <t>Narayana Hrudayalaya Ltd. **</t>
+  </si>
+  <si>
+    <t>INE410P08016</t>
+  </si>
+  <si>
+    <t>INE896L07975</t>
+  </si>
+  <si>
+    <t>Avanse Financial Services Ltd **</t>
+  </si>
+  <si>
+    <t>INE087P07444</t>
+  </si>
+  <si>
+    <t>INE087P07410</t>
+  </si>
+  <si>
+    <t>Hampi Expressways Private Ltd. **</t>
+  </si>
+  <si>
+    <t>INE03ST08010</t>
+  </si>
+  <si>
+    <t>CARE AA+(CE)</t>
+  </si>
+  <si>
+    <t>G R Infraprojects Ltd. **</t>
+  </si>
+  <si>
+    <t>INE201P08183</t>
+  </si>
+  <si>
+    <t>INE852O07139</t>
+  </si>
+  <si>
+    <t>INE412L08011</t>
   </si>
   <si>
     <t>Yes Bank Ltd. **</t>
   </si>
   <si>
-    <t>INE528G08279</t>
+    <t>INE528G08345</t>
   </si>
   <si>
     <t>ICRA A</t>
   </si>
   <si>
-    <t>IIFL Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE477L07AV2</t>
+    <t>INE153A08089</t>
+  </si>
+  <si>
+    <t>BWR AA+(CE)</t>
+  </si>
+  <si>
+    <t>INE670K07265</t>
+  </si>
+  <si>
+    <t>Bahadur Chand Investments Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE087M08134</t>
+  </si>
+  <si>
+    <t>INE087M08126</t>
+  </si>
+  <si>
+    <t>DME Development Ltd. **</t>
+  </si>
+  <si>
+    <t>INE0J7Q07090</t>
   </si>
   <si>
     <t>Indostar Capital Finance Ltd. **</t>
   </si>
   <si>
-    <t>INE896L07892</t>
-  </si>
-  <si>
-    <t>CRISIL AA-</t>
-  </si>
-  <si>
-    <t>JM Financial Asset Recosntruction Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE265J07514</t>
-  </si>
-  <si>
-    <t>INE265J07522</t>
-  </si>
-  <si>
-    <t>INE477L07AW0</t>
-  </si>
-  <si>
-    <t>State Bank of India ( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE062A08256</t>
-  </si>
-  <si>
-    <t>CRISIL AAA</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd. **</t>
-  </si>
-  <si>
-    <t>INE775A08089</t>
-  </si>
-  <si>
-    <t>FITCH AAA</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE233A08071</t>
-  </si>
-  <si>
-    <t>CRISIL AA+</t>
-  </si>
-  <si>
-    <t>Prism Johnson Ltd. **</t>
-  </si>
-  <si>
-    <t>INE010A08156</t>
-  </si>
-  <si>
-    <t>FITCH A+</t>
-  </si>
-  <si>
-    <t>INE010A08149</t>
-  </si>
-  <si>
-    <t>Eris Lifesciences Ltd. **</t>
-  </si>
-  <si>
-    <t>INE406M08029</t>
-  </si>
-  <si>
-    <t>INE406M08011</t>
-  </si>
-  <si>
-    <t>Ess Kay Fincorp Ltd **</t>
-  </si>
-  <si>
-    <t>INE124N07689</t>
-  </si>
-  <si>
-    <t>Aptus Value Housing Finance India Ltd. **</t>
-  </si>
-  <si>
-    <t>INE852O07147</t>
-  </si>
-  <si>
-    <t>CARE AA-</t>
-  </si>
-  <si>
-    <t>INE670K07265</t>
-  </si>
-  <si>
-    <t>Narayana Hrudayalaya Ltd. **</t>
-  </si>
-  <si>
-    <t>INE410P08016</t>
-  </si>
-  <si>
-    <t>Creamline Dairy Products Ltd **</t>
-  </si>
-  <si>
-    <t>INE412L08029</t>
-  </si>
-  <si>
-    <t>Avanse Financial Services Ltd **</t>
-  </si>
-  <si>
-    <t>INE087P07444</t>
-  </si>
-  <si>
-    <t>INE087P07410</t>
-  </si>
-  <si>
-    <t>G R Infraprojects Ltd. **</t>
-  </si>
-  <si>
-    <t>INE201P08183</t>
-  </si>
-  <si>
-    <t>INE896L07975</t>
-  </si>
-  <si>
-    <t>INE670K07273</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd. **</t>
-  </si>
-  <si>
-    <t>INE093I07082</t>
-  </si>
-  <si>
-    <t>Hampi Expressways Private Ltd. **</t>
-  </si>
-  <si>
-    <t>INE03ST08010</t>
-  </si>
-  <si>
-    <t>CARE AA+(CE)</t>
-  </si>
-  <si>
-    <t>INE852O07139</t>
-  </si>
-  <si>
-    <t>INE412L08011</t>
-  </si>
-  <si>
-    <t>Astec LifeSciences Ltd. **</t>
-  </si>
-  <si>
-    <t>INE563J08015</t>
-  </si>
-  <si>
-    <t>INE528G08345</t>
-  </si>
-  <si>
-    <t>INE153A08089</t>
-  </si>
-  <si>
-    <t>BWR AA+(CE)</t>
-  </si>
-  <si>
-    <t>Bahadur Chand Investments Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE087M08126</t>
-  </si>
-  <si>
-    <t>INE087M08134</t>
-  </si>
-  <si>
-    <t>DME Development Ltd. **</t>
-  </si>
-  <si>
-    <t>INE0J7Q07090</t>
+    <t>INE896L07AG4</t>
+  </si>
+  <si>
+    <t>Tyger Capital Private Ltd. **</t>
+  </si>
+  <si>
+    <t>INE01EQ07103</t>
+  </si>
+  <si>
+    <t>CRISIL A+</t>
+  </si>
+  <si>
+    <t>INE01EQ07095</t>
+  </si>
+  <si>
+    <t>Tata Projects Ltd. **</t>
+  </si>
+  <si>
+    <t>INE725H08246</t>
+  </si>
+  <si>
+    <t>Jhajjar Power Ltd. **</t>
+  </si>
+  <si>
+    <t>INE165K07027</t>
+  </si>
+  <si>
+    <t>FITCH AA(CE)</t>
+  </si>
+  <si>
+    <t>INE062A08264</t>
+  </si>
+  <si>
+    <t>INE0J7Q07074</t>
+  </si>
+  <si>
+    <t>INE0J7Q07082</t>
+  </si>
+  <si>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
+  </si>
+  <si>
+    <t>INE0J7Q07066</t>
+  </si>
+  <si>
+    <t>INE0J7Q07041</t>
+  </si>
+  <si>
+    <t>INE729N08063</t>
+  </si>
+  <si>
+    <t>Sheela Foam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE916U08012</t>
+  </si>
+  <si>
+    <t>INE916U08038</t>
+  </si>
+  <si>
+    <t>INE916U08020</t>
+  </si>
+  <si>
+    <t>INE0J7Q07017</t>
+  </si>
+  <si>
+    <t>INE0J7Q07108</t>
+  </si>
+  <si>
+    <t>INE883F07330</t>
+  </si>
+  <si>
+    <t>The Great Eastern Shipping Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE017A08250</t>
+  </si>
+  <si>
+    <t>Indian Railway Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE053F07AA7</t>
+  </si>
+  <si>
+    <t>Zero Coupon Bonds / Deep Discount Bonds</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>Privately Placed/unlisted</t>
+  </si>
+  <si>
+    <t>Millennia Realtors Pvt Ltd **</t>
+  </si>
+  <si>
+    <t>INE487H07021</t>
+  </si>
+  <si>
+    <t>Securitized Debt Instruments</t>
+  </si>
+  <si>
+    <t>Term Deposits</t>
+  </si>
+  <si>
+    <t>Deposits (maturity not exceeding 91 days)</t>
+  </si>
+  <si>
+    <t>Deposits (Placed as Margin)</t>
+  </si>
+  <si>
+    <t>Money Market Instruments</t>
+  </si>
+  <si>
+    <t>Certificate of Deposits</t>
+  </si>
+  <si>
+    <t>Export-Import Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE514E16CL5</t>
+  </si>
+  <si>
+    <t>CRISIL A1+</t>
   </si>
   <si>
     <t>NABARD **</t>
   </si>
   <si>
-    <t>INE261F08DQ4</t>
-  </si>
-  <si>
-    <t>INE896L07AG4</t>
-  </si>
-  <si>
-    <t>Tyger Capital Private Ltd. **</t>
-  </si>
-  <si>
-    <t>INE01EQ07103</t>
-  </si>
-  <si>
-    <t>CRISIL A+</t>
-  </si>
-  <si>
-    <t>INE01EQ07095</t>
-  </si>
-  <si>
-    <t>INE896L07876</t>
-  </si>
-  <si>
-    <t>INE233A08063</t>
-  </si>
-  <si>
-    <t>Jhajjar Power Ltd. **</t>
-  </si>
-  <si>
-    <t>INE165K07019</t>
-  </si>
-  <si>
-    <t>FITCH AA(CE)</t>
-  </si>
-  <si>
-    <t>INE165K07027</t>
-  </si>
-  <si>
-    <t>INE062A08264</t>
-  </si>
-  <si>
-    <t>INE0J7Q07074</t>
-  </si>
-  <si>
-    <t>INE0J7Q07082</t>
-  </si>
-  <si>
-    <t>INE0J7Q07066</t>
-  </si>
-  <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
-    <t>INE0J7Q07041</t>
-  </si>
-  <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
-    <t>INE729N08063</t>
-  </si>
-  <si>
-    <t>Sheela Foam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE916U08012</t>
-  </si>
-  <si>
-    <t>INE916U08038</t>
-  </si>
-  <si>
-    <t>INE916U08046</t>
-  </si>
-  <si>
-    <t>INE916U08020</t>
-  </si>
-  <si>
-    <t>INE0J7Q07017</t>
-  </si>
-  <si>
-    <t>INE0J7Q07108</t>
-  </si>
-  <si>
-    <t>The Great Eastern Shipping Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE017A08250</t>
-  </si>
-  <si>
-    <t>Indian Railway Finance Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE053F07AA7</t>
-  </si>
-  <si>
-    <t>Zero Coupon Bonds / Deep Discount Bonds</t>
-  </si>
-  <si>
-    <t>Nil</t>
-  </si>
-  <si>
-    <t>Privately Placed/unlisted</t>
-  </si>
-  <si>
-    <t>Millennia Realtors Pvt Ltd **</t>
-  </si>
-  <si>
-    <t>INE487H07021</t>
-  </si>
-  <si>
-    <t>Securitized Debt Instruments</t>
-  </si>
-  <si>
-    <t>Term Deposits</t>
-  </si>
-  <si>
-    <t>Deposits (maturity not exceeding 91 days)</t>
-  </si>
-  <si>
-    <t>Deposits (Placed as Margin)</t>
-  </si>
-  <si>
-    <t>Money Market Instruments</t>
-  </si>
-  <si>
-    <t>Certificate of Deposits</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE040A16EP6</t>
-  </si>
-  <si>
-    <t>CRISIL A1+</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A16YV8</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE238AD6819</t>
-  </si>
-  <si>
-    <t>Punjab National Bank **</t>
-  </si>
-  <si>
-    <t>INE160A16OP1</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A16PK9</t>
-  </si>
-  <si>
-    <t>INE040A16EU6</t>
+    <t>INE261F16967</t>
+  </si>
+  <si>
+    <t>Small Industries Development Bank Of India. **</t>
+  </si>
+  <si>
+    <t>INE556F16BI1</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE095A16Z18</t>
   </si>
   <si>
     <t>Commercial Papers</t>
@@ -609,6 +597,12 @@
     <t>INE0FDU25010</t>
   </si>
   <si>
+    <t>Nexus Select Trust</t>
+  </si>
+  <si>
+    <t>INE0NDH25011</t>
+  </si>
+  <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
   </si>
   <si>
@@ -636,6 +630,18 @@
     <t> IDFC FIRST Bank Ltd- MD -05-Oct-2026 (Pay float/receive fixed)</t>
   </si>
   <si>
+    <t> DBS Bank India Ltd- MD -29-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -06-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -651,7 +657,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -664,9 +670,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - CRISIL Credit Risk Debt B-II Index</t>
   </si>
   <si>
     <t>Mahanagar Telephone Nigam Ltd. ** #</t>
@@ -884,6 +887,17 @@
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -895,17 +909,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -985,13 +988,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>165</xdr:row>
+      <xdr:row>164</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1009,7 +1012,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30175200"/>
+          <a:off x="666750" y="30165675"/>
           <a:ext cx="4438650" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1026,13 +1029,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>170</xdr:row>
+      <xdr:row>169</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>180</xdr:row>
+      <xdr:row>179</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1050,7 +1053,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="33032700"/>
+          <a:off x="666750" y="33023175"/>
           <a:ext cx="4438650" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1386,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="27" customWidth="1" collapsed="1"/>
@@ -1402,43 +1405,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -1486,10 +1489,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="13">
-        <v>506638.72000000003</v>
+        <v>512225.25000000006</v>
       </c>
       <c r="H5" s="14">
-        <v>0.81512062437580002</v>
+        <v>0.83486364689109993</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>13</v>
@@ -1523,10 +1526,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="13">
-        <v>485617.78</v>
+        <v>491063.23000000004</v>
       </c>
       <c r="H7" s="14">
-        <v>0.7813004660234999</v>
+        <v>0.80037217816159989</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>13</v>
@@ -1560,10 +1563,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="13">
-        <v>67971.69</v>
+        <v>85166.92</v>
       </c>
       <c r="H9" s="14">
-        <v>0.10935825511479999</v>
+        <v>0.13881151978710002</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>13</v>
@@ -1586,16 +1589,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="19">
-        <v>36170730</v>
+        <v>47530230</v>
       </c>
       <c r="G10" s="20">
-        <v>37041.14</v>
+        <v>50105.42</v>
       </c>
       <c r="H10" s="21">
-        <v>5.9594728891899998E-2</v>
+        <v>8.1665622048799999E-2</v>
       </c>
       <c r="I10" s="20">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="15" t="s">
         <v>13</v>
@@ -1609,22 +1612,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="18">
-        <v>7.17</v>
+        <v>6.79</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="19">
-        <v>15000000</v>
+        <v>23971830</v>
       </c>
       <c r="G11" s="20">
-        <v>15324.27</v>
+        <v>24833.11</v>
       </c>
       <c r="H11" s="21">
-        <v>2.4654903064900001E-2</v>
+        <v>4.04748902525E-2</v>
       </c>
       <c r="I11" s="20">
-        <v>6.78</v>
+        <v>6.37</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>13</v>
@@ -1638,22 +1641,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="18">
-        <v>7.18</v>
+        <v>7.34</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="19">
-        <v>9130230</v>
+        <v>4801500</v>
       </c>
       <c r="G12" s="20">
-        <v>9379.9</v>
+        <v>5110.88</v>
       </c>
       <c r="H12" s="21">
-        <v>1.50911283381E-2</v>
+        <v>8.3301007040000007E-3</v>
       </c>
       <c r="I12" s="20">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>13</v>
@@ -1661,28 +1664,28 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="18">
-        <v>6.79</v>
+        <v>7.1400000000000006</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="19">
-        <v>3701100</v>
+        <v>2000000</v>
       </c>
       <c r="G13" s="20">
-        <v>3725.51</v>
+        <v>2075.5100000000002</v>
       </c>
       <c r="H13" s="21">
-        <v>5.9938964738000004E-3</v>
+        <v>3.3828239583000002E-3</v>
       </c>
       <c r="I13" s="20">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>13</v>
@@ -1690,28 +1693,28 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="18">
-        <v>8.06</v>
+        <v>7.12</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="19">
-        <v>2500000</v>
+        <v>1653600</v>
       </c>
       <c r="G14" s="20">
-        <v>2500.87</v>
+        <v>1709.23</v>
       </c>
       <c r="H14" s="21">
-        <v>4.0235983461E-3</v>
+        <v>2.7858329732E-3</v>
       </c>
       <c r="I14" s="20">
-        <v>6.64</v>
+        <v>6.83</v>
       </c>
       <c r="J14" s="15" t="s">
         <v>13</v>
@@ -1719,36 +1722,57 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="18">
+        <v>7.13</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="19">
+        <v>998400</v>
+      </c>
+      <c r="G15" s="20">
+        <v>1031.3</v>
+      </c>
+      <c r="H15" s="21">
+        <v>1.6808911295E-3</v>
+      </c>
+      <c r="I15" s="20">
+        <v>6.75</v>
       </c>
       <c r="J15" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="13">
-        <v>417646.09</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0.67194221090869988</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>13</v>
+      <c r="B16" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="18">
+        <v>7.29</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="19">
+        <v>288800</v>
+      </c>
+      <c r="G16" s="20">
+        <v>301.47000000000003</v>
+      </c>
+      <c r="H16" s="21">
+        <v>4.9135872079999999E-4</v>
+      </c>
+      <c r="I16" s="20">
+        <v>6.88</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>13</v>
@@ -1756,57 +1780,36 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="18">
-        <v>8.6</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="19">
-        <v>25000</v>
-      </c>
-      <c r="G17" s="20">
-        <v>23298.35</v>
-      </c>
-      <c r="H17" s="21">
-        <v>3.7484236497000001E-2</v>
-      </c>
-      <c r="I17" s="20">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="18">
-        <v>10.81</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="19">
-        <v>18500</v>
-      </c>
-      <c r="G18" s="20">
-        <v>18429.29</v>
-      </c>
-      <c r="H18" s="21">
-        <v>2.9650505929900001E-2</v>
-      </c>
-      <c r="I18" s="20">
-        <v>11.49</v>
+      <c r="C18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="13">
+        <v>405896.31</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0.66156065837449984</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>13</v>
@@ -1814,28 +1817,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="18">
+        <v>8.6</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="18">
-        <v>8.5</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>32</v>
-      </c>
       <c r="F19" s="19">
-        <v>17500</v>
+        <v>25000</v>
       </c>
       <c r="G19" s="20">
-        <v>17514.37</v>
+        <v>21932.43</v>
       </c>
       <c r="H19" s="21">
-        <v>2.8178509944899999E-2</v>
+        <v>3.5747141506699998E-2</v>
       </c>
       <c r="I19" s="20">
-        <v>8.3800000000000008</v>
+        <v>8.44</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>13</v>
@@ -1843,28 +1846,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="18">
+        <v>9.4</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="18">
-        <v>8.5</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>35</v>
-      </c>
       <c r="F20" s="19">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="G20" s="20">
-        <v>15123.57</v>
+        <v>20092.48</v>
       </c>
       <c r="H20" s="21">
-        <v>2.43320009596E-2</v>
+        <v>3.2748251141299999E-2</v>
       </c>
       <c r="I20" s="20">
-        <v>8.0399999999999991</v>
+        <v>9.06</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>13</v>
@@ -1872,28 +1875,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="18">
+        <v>10.81</v>
+      </c>
+      <c r="E21" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="18">
-        <v>8.5</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>32</v>
-      </c>
       <c r="F21" s="19">
-        <v>15000</v>
+        <v>18500</v>
       </c>
       <c r="G21" s="20">
-        <v>15037.28</v>
+        <v>18662.91</v>
       </c>
       <c r="H21" s="21">
-        <v>2.4193170752E-2</v>
+        <v>3.04182292932E-2</v>
       </c>
       <c r="I21" s="20">
-        <v>8.1199999999999992</v>
+        <v>10.62</v>
       </c>
       <c r="J21" s="15" t="s">
         <v>13</v>
@@ -1901,28 +1904,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>39</v>
-      </c>
       <c r="D22" s="18">
-        <v>8.8605999999999998</v>
+        <v>8.5</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" s="19">
-        <v>10000</v>
+        <v>17500</v>
       </c>
       <c r="G22" s="20">
-        <v>10017.92</v>
+        <v>17686.150000000001</v>
       </c>
       <c r="H22" s="21">
-        <v>1.61176256038E-2</v>
+        <v>2.88262316012E-2</v>
       </c>
       <c r="I22" s="20">
-        <v>9.0500000000000007</v>
+        <v>7.5</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>13</v>
@@ -1930,28 +1933,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="D23" s="18">
+        <v>8.5</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="18">
-        <v>8.85</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>35</v>
-      </c>
       <c r="F23" s="19">
-        <v>99</v>
+        <v>15000</v>
       </c>
       <c r="G23" s="20">
-        <v>9959.8700000000008</v>
+        <v>15249.95</v>
       </c>
       <c r="H23" s="21">
-        <v>1.60242301518E-2</v>
+        <v>2.4855527664699999E-2</v>
       </c>
       <c r="I23" s="20">
-        <v>8.57</v>
+        <v>7.4</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>13</v>
@@ -1965,22 +1968,22 @@
         <v>43</v>
       </c>
       <c r="D24" s="18">
-        <v>8.32</v>
+        <v>8.5</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F24" s="19">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="G24" s="20">
-        <v>9900.17</v>
+        <v>15070.47</v>
       </c>
       <c r="H24" s="21">
-        <v>1.5928180048799999E-2</v>
+        <v>2.45629975184E-2</v>
       </c>
       <c r="I24" s="20">
-        <v>8.7100000000000009</v>
+        <v>6.95</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>13</v>
@@ -1988,28 +1991,28 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="16" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="18">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F25" s="19">
-        <v>95</v>
+        <v>12500</v>
       </c>
       <c r="G25" s="20">
-        <v>9702.25</v>
+        <v>12592.94</v>
       </c>
       <c r="H25" s="21">
-        <v>1.5609750628299999E-2</v>
+        <v>2.0524930806299999E-2</v>
       </c>
       <c r="I25" s="20">
-        <v>8.64</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>13</v>
@@ -2017,28 +2020,28 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D26" s="18">
-        <v>7.266</v>
+        <v>8.32</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F26" s="19">
-        <v>900</v>
+        <v>10000</v>
       </c>
       <c r="G26" s="20">
-        <v>9463.64</v>
+        <v>10190.99</v>
       </c>
       <c r="H26" s="21">
-        <v>1.5225855903200001E-2</v>
+        <v>1.66100501231E-2</v>
       </c>
       <c r="I26" s="20">
-        <v>8.74</v>
+        <v>7.41</v>
       </c>
       <c r="J26" s="15" t="s">
         <v>13</v>
@@ -2046,28 +2049,28 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D27" s="18">
-        <v>8.75</v>
+        <v>8.8605999999999998</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F27" s="19">
         <v>10000</v>
       </c>
       <c r="G27" s="20">
-        <v>8997.2199999999993</v>
+        <v>10142.18</v>
       </c>
       <c r="H27" s="21">
-        <v>1.44754423508E-2</v>
+        <v>1.6530495875099999E-2</v>
       </c>
       <c r="I27" s="20">
-        <v>8.89</v>
+        <v>8.06</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>13</v>
@@ -2081,22 +2084,22 @@
         <v>52</v>
       </c>
       <c r="D28" s="18">
-        <v>9.75</v>
+        <v>8.85</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F28" s="19">
-        <v>9000</v>
+        <v>99</v>
       </c>
       <c r="G28" s="20">
-        <v>8956.75</v>
+        <v>10042.790000000001</v>
       </c>
       <c r="H28" s="21">
-        <v>1.4410330999600001E-2</v>
+        <v>1.6368502498399998E-2</v>
       </c>
       <c r="I28" s="20">
-        <v>10.199999999999999</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>13</v>
@@ -2110,22 +2113,22 @@
         <v>55</v>
       </c>
       <c r="D29" s="18">
-        <v>7.95</v>
+        <v>9.6</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>56</v>
       </c>
       <c r="F29" s="19">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G29" s="20">
-        <v>8702.24</v>
+        <v>9981.66</v>
       </c>
       <c r="H29" s="21">
-        <v>1.40008550911E-2</v>
+        <v>1.6268868177899999E-2</v>
       </c>
       <c r="I29" s="20">
-        <v>9.68</v>
+        <v>9.76</v>
       </c>
       <c r="J29" s="15" t="s">
         <v>13</v>
@@ -2133,28 +2136,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>58</v>
-      </c>
       <c r="D30" s="18">
-        <v>9.9500000000000011</v>
+        <v>9.5</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F30" s="19">
-        <v>8500</v>
+        <v>95</v>
       </c>
       <c r="G30" s="20">
-        <v>8480.17</v>
+        <v>9805.76</v>
       </c>
       <c r="H30" s="21">
-        <v>1.3643571231999999E-2</v>
+        <v>1.5982172987700001E-2</v>
       </c>
       <c r="I30" s="20">
-        <v>10.47</v>
+        <v>8.11</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>13</v>
@@ -2162,28 +2165,28 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="18">
+        <v>9.75</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="18">
-        <v>8.85</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>62</v>
-      </c>
       <c r="F31" s="19">
-        <v>800</v>
+        <v>9500</v>
       </c>
       <c r="G31" s="20">
-        <v>7998.27</v>
+        <v>9516.9599999999991</v>
       </c>
       <c r="H31" s="21">
-        <v>1.28682522258E-2</v>
+        <v>1.55114647959E-2</v>
       </c>
       <c r="I31" s="20">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>13</v>
@@ -2191,28 +2194,28 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D32" s="18">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="F32" s="19">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="G32" s="20">
-        <v>7987.44</v>
+        <v>9015.42</v>
       </c>
       <c r="H32" s="21">
-        <v>1.28508280614E-2</v>
+        <v>1.4694016781600001E-2</v>
       </c>
       <c r="I32" s="20">
-        <v>9.1999999999999993</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>13</v>
@@ -2220,28 +2223,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D33" s="18">
         <v>9.9500000000000011</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F33" s="19">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="G33" s="20">
-        <v>7522.43</v>
+        <v>8585.02</v>
       </c>
       <c r="H33" s="21">
-        <v>1.21026830291E-2</v>
+        <v>1.39925181467E-2</v>
       </c>
       <c r="I33" s="20">
-        <v>9.5</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="J33" s="15" t="s">
         <v>13</v>
@@ -2249,28 +2252,28 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="18">
+        <v>9.66</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="18">
-        <v>10.200000000000001</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>50</v>
-      </c>
       <c r="F34" s="19">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="G34" s="20">
-        <v>7519.44</v>
+        <v>7874.18</v>
       </c>
       <c r="H34" s="21">
-        <v>1.20978724795E-2</v>
+        <v>1.28339370835E-2</v>
       </c>
       <c r="I34" s="20">
-        <v>9.8800000000000008</v>
+        <v>8.81</v>
       </c>
       <c r="J34" s="15" t="s">
         <v>13</v>
@@ -2278,7 +2281,7 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>70</v>
@@ -2287,19 +2290,19 @@
         <v>10.200000000000001</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F35" s="19">
         <v>7500</v>
       </c>
       <c r="G35" s="20">
-        <v>7513.7</v>
+        <v>7521.51</v>
       </c>
       <c r="H35" s="21">
-        <v>1.20886375115E-2</v>
+        <v>1.22591287109E-2</v>
       </c>
       <c r="I35" s="20">
-        <v>9.77</v>
+        <v>8.35</v>
       </c>
       <c r="J35" s="15" t="s">
         <v>13</v>
@@ -2307,86 +2310,86 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D36" s="18">
-        <v>8.5</v>
+        <v>6.24</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="F36" s="19">
-        <v>7500</v>
+        <v>750</v>
       </c>
       <c r="G36" s="20">
-        <v>7471.22</v>
+        <v>7505.27</v>
       </c>
       <c r="H36" s="21">
-        <v>1.20202923125E-2</v>
+        <v>1.2232659524500001E-2</v>
       </c>
       <c r="I36" s="20">
-        <v>9.25</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>13</v>
+        <v>6.22</v>
+      </c>
+      <c r="J36" s="15">
+        <v>5.76</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D37" s="18">
-        <v>6.24</v>
+        <v>8.6</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F37" s="19">
-        <v>750</v>
+        <v>7000</v>
       </c>
       <c r="G37" s="20">
-        <v>7424.38</v>
+        <v>7073.21</v>
       </c>
       <c r="H37" s="21">
-        <v>1.19449323992E-2</v>
+        <v>1.1528455295499999E-2</v>
       </c>
       <c r="I37" s="20">
-        <v>6.45</v>
-      </c>
-      <c r="J37" s="15">
-        <v>7.74</v>
+        <v>8.02</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D38" s="18">
-        <v>8.15</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="F38" s="19">
         <v>7000</v>
       </c>
       <c r="G38" s="20">
-        <v>7015.4</v>
+        <v>7068.59</v>
       </c>
       <c r="H38" s="21">
-        <v>1.12869328824E-2</v>
+        <v>1.15209252683E-2</v>
       </c>
       <c r="I38" s="20">
-        <v>7.89</v>
+        <v>7.28</v>
       </c>
       <c r="J38" s="15" t="s">
         <v>13</v>
@@ -2394,28 +2397,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D39" s="18">
-        <v>8.3000000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F39" s="19">
         <v>7000</v>
       </c>
       <c r="G39" s="20">
-        <v>7010.57</v>
+        <v>7043.98</v>
       </c>
       <c r="H39" s="21">
-        <v>1.1279161994600001E-2</v>
+        <v>1.1480814019699999E-2</v>
       </c>
       <c r="I39" s="20">
-        <v>8.19</v>
+        <v>6.94</v>
       </c>
       <c r="J39" s="15" t="s">
         <v>13</v>
@@ -2423,28 +2426,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D40" s="18">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F40" s="19">
         <v>7000</v>
       </c>
       <c r="G40" s="20">
-        <v>6958.19</v>
+        <v>7033.94</v>
       </c>
       <c r="H40" s="21">
-        <v>1.11948888891E-2</v>
+        <v>1.14644500645E-2</v>
       </c>
       <c r="I40" s="20">
-        <v>8.84</v>
+        <v>7.99</v>
       </c>
       <c r="J40" s="15" t="s">
         <v>13</v>
@@ -2452,28 +2455,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D41" s="18">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="F41" s="19">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="G41" s="20">
-        <v>6954.92</v>
+        <v>7004.21</v>
       </c>
       <c r="H41" s="21">
-        <v>1.1189627853300001E-2</v>
+        <v>1.1415993850699999E-2</v>
       </c>
       <c r="I41" s="20">
-        <v>8.94</v>
+        <v>7.79</v>
       </c>
       <c r="J41" s="15" t="s">
         <v>13</v>
@@ -2481,28 +2484,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D42" s="18">
         <v>8.73</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F42" s="19">
         <v>6500</v>
       </c>
       <c r="G42" s="20">
-        <v>6525.38</v>
+        <v>6631.18</v>
       </c>
       <c r="H42" s="21">
-        <v>1.0498549775099999E-2</v>
+        <v>1.08080012026E-2</v>
       </c>
       <c r="I42" s="20">
-        <v>8.5</v>
+        <v>7.61</v>
       </c>
       <c r="J42" s="15" t="s">
         <v>13</v>
@@ -2510,28 +2513,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D43" s="18">
         <v>8.73</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F43" s="19">
         <v>6500</v>
       </c>
       <c r="G43" s="20">
-        <v>6521.11</v>
+        <v>6606.46</v>
       </c>
       <c r="H43" s="21">
-        <v>1.0491679859800001E-2</v>
+        <v>1.0767710667599999E-2</v>
       </c>
       <c r="I43" s="20">
-        <v>8.5299999999999994</v>
+        <v>7.6</v>
       </c>
       <c r="J43" s="15" t="s">
         <v>13</v>
@@ -2539,28 +2542,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" s="18">
         <v>9.25</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F44" s="19">
         <v>6500</v>
       </c>
       <c r="G44" s="20">
-        <v>6458.14</v>
+        <v>6498.28</v>
       </c>
       <c r="H44" s="21">
-        <v>1.03903687209E-2</v>
+        <v>1.0591390680800001E-2</v>
       </c>
       <c r="I44" s="20">
-        <v>9.81</v>
+        <v>9.15</v>
       </c>
       <c r="J44" s="15" t="s">
         <v>13</v>
@@ -2568,28 +2571,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D45" s="18">
         <v>8.75</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="F45" s="19">
         <v>6000</v>
       </c>
       <c r="G45" s="20">
-        <v>5933.64</v>
+        <v>5969.03</v>
       </c>
       <c r="H45" s="21">
-        <v>9.5465114502999993E-3</v>
+        <v>9.7287788022999994E-3</v>
       </c>
       <c r="I45" s="20">
-        <v>9.8800000000000008</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="J45" s="15" t="s">
         <v>13</v>
@@ -2597,28 +2600,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="16" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D46" s="18">
-        <v>8.7900000000000009</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F46" s="19">
-        <v>5114</v>
+        <v>5000</v>
       </c>
       <c r="G46" s="20">
-        <v>5112.09</v>
+        <v>5077.1899999999996</v>
       </c>
       <c r="H46" s="21">
-        <v>8.2247365394000002E-3</v>
+        <v>8.2751901811999994E-3</v>
       </c>
       <c r="I46" s="20">
-        <v>9.14</v>
+        <v>7.76</v>
       </c>
       <c r="J46" s="15" t="s">
         <v>13</v>
@@ -2626,28 +2629,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D47" s="18">
-        <v>8.25</v>
+        <v>8.65</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="F47" s="19">
         <v>5000</v>
       </c>
       <c r="G47" s="20">
-        <v>5013.7700000000004</v>
+        <v>5061.01</v>
       </c>
       <c r="H47" s="21">
-        <v>8.0665515119999996E-3</v>
+        <v>8.2488187872999993E-3</v>
       </c>
       <c r="I47" s="20">
-        <v>8.09</v>
+        <v>7.64</v>
       </c>
       <c r="J47" s="15" t="s">
         <v>13</v>
@@ -2655,28 +2658,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="16" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D48" s="18">
-        <v>8.65</v>
+        <v>8.6</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F48" s="19">
         <v>5000</v>
       </c>
       <c r="G48" s="20">
-        <v>5002.63</v>
+        <v>5056.75</v>
       </c>
       <c r="H48" s="21">
-        <v>8.0486285949999993E-3</v>
+        <v>8.2418755154999995E-3</v>
       </c>
       <c r="I48" s="20">
-        <v>8.57</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="J48" s="15" t="s">
         <v>13</v>
@@ -2684,28 +2687,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D49" s="18">
-        <v>9.4</v>
+        <v>8.25</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F49" s="19">
         <v>5000</v>
       </c>
       <c r="G49" s="20">
-        <v>4997.3599999999997</v>
+        <v>5054.13</v>
       </c>
       <c r="H49" s="21">
-        <v>8.0401498002999998E-3</v>
+        <v>8.2376052404000005E-3</v>
       </c>
       <c r="I49" s="20">
-        <v>9.66</v>
+        <v>7.55</v>
       </c>
       <c r="J49" s="15" t="s">
         <v>13</v>
@@ -2713,28 +2716,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="16" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D50" s="18">
-        <v>9.4</v>
+        <v>9.9500000000000011</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F50" s="19">
         <v>5000</v>
       </c>
       <c r="G50" s="20">
-        <v>4994.32</v>
+        <v>5046.97</v>
       </c>
       <c r="H50" s="21">
-        <v>8.0352588068000001E-3</v>
+        <v>8.2259353281000005E-3</v>
       </c>
       <c r="I50" s="20">
-        <v>9.6999999999999993</v>
+        <v>9.6</v>
       </c>
       <c r="J50" s="15" t="s">
         <v>13</v>
@@ -2742,28 +2745,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D51" s="18">
-        <v>8.5500000000000007</v>
+        <v>9.4</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F51" s="19">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G51" s="20">
-        <v>4993.5</v>
+        <v>5021.38</v>
       </c>
       <c r="H51" s="21">
-        <v>8.0339395255999996E-3</v>
+        <v>8.184226801E-3</v>
       </c>
       <c r="I51" s="20">
-        <v>8.4700000000000006</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="J51" s="15" t="s">
         <v>13</v>
@@ -2771,28 +2774,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D52" s="18">
-        <v>9.9500000000000011</v>
+        <v>9.4</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="F52" s="19">
         <v>5000</v>
       </c>
       <c r="G52" s="20">
-        <v>4990.92</v>
+        <v>5019.12</v>
       </c>
       <c r="H52" s="21">
-        <v>8.0297886165999997E-3</v>
+        <v>8.1805432813000008E-3</v>
       </c>
       <c r="I52" s="20">
-        <v>10.44</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="J52" s="15" t="s">
         <v>13</v>
@@ -2800,28 +2803,28 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="16" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D53" s="18">
-        <v>8.6</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="F53" s="19">
         <v>5000</v>
       </c>
       <c r="G53" s="20">
-        <v>4988.47</v>
+        <v>5004.41</v>
       </c>
       <c r="H53" s="21">
-        <v>8.0258468620000006E-3</v>
+        <v>8.1565678051000005E-3</v>
       </c>
       <c r="I53" s="20">
-        <v>9.0299999999999994</v>
+        <v>7.42</v>
       </c>
       <c r="J53" s="15" t="s">
         <v>13</v>
@@ -2829,28 +2832,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D54" s="18">
         <v>8.0500000000000007</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F54" s="19">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="G54" s="20">
-        <v>4980.82</v>
+        <v>5000.07</v>
       </c>
       <c r="H54" s="21">
-        <v>8.0135389341999992E-3</v>
+        <v>8.1494941433000005E-3</v>
       </c>
       <c r="I54" s="20">
-        <v>8.5500000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="J54" s="15" t="s">
         <v>13</v>
@@ -2858,28 +2861,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="16" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D55" s="18">
-        <v>8.1999999999999993</v>
+        <v>8.75</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="F55" s="19">
         <v>5000</v>
       </c>
       <c r="G55" s="20">
-        <v>4962.51</v>
+        <v>4979.16</v>
       </c>
       <c r="H55" s="21">
-        <v>7.9840803515000003E-3</v>
+        <v>8.1154134359000003E-3</v>
       </c>
       <c r="I55" s="20">
-        <v>8.36</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="J55" s="15" t="s">
         <v>13</v>
@@ -2887,28 +2890,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D56" s="18">
-        <v>8.75</v>
+        <v>8.65</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F56" s="19">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G56" s="20">
-        <v>4951.95</v>
+        <v>4953.3</v>
       </c>
       <c r="H56" s="21">
-        <v>7.9670905845000001E-3</v>
+        <v>8.0732648423000007E-3</v>
       </c>
       <c r="I56" s="20">
-        <v>9.9</v>
+        <v>7.64</v>
       </c>
       <c r="J56" s="15" t="s">
         <v>13</v>
@@ -2916,28 +2919,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D57" s="18">
-        <v>8.65</v>
+        <v>8</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="F57" s="19">
-        <v>4900</v>
+        <v>450</v>
       </c>
       <c r="G57" s="20">
-        <v>4900.49</v>
+        <v>4476.32</v>
       </c>
       <c r="H57" s="21">
-        <v>7.8842976480999992E-3</v>
+        <v>7.2958465828E-3</v>
       </c>
       <c r="I57" s="20">
-        <v>8.58</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="J57" s="15" t="s">
         <v>13</v>
@@ -2945,28 +2948,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="16" t="s">
-        <v>112</v>
+        <v>217</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D58" s="18">
-        <v>8.4</v>
+        <v>7.05</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="F58" s="19">
-        <v>4900</v>
+        <v>411</v>
       </c>
       <c r="G58" s="20">
-        <v>4888.01</v>
+        <v>4052.08</v>
       </c>
       <c r="H58" s="21">
-        <v>7.8642188326000003E-3</v>
+        <v>6.6043879841999999E-3</v>
       </c>
       <c r="I58" s="20">
-        <v>8.52</v>
+        <v>7.51</v>
       </c>
       <c r="J58" s="15" t="s">
         <v>13</v>
@@ -2974,28 +2977,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D59" s="18">
-        <v>8</v>
+        <v>8.7900000000000009</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F59" s="19">
-        <v>450</v>
+        <v>3614</v>
       </c>
       <c r="G59" s="20">
-        <v>4404.83</v>
+        <v>3630.44</v>
       </c>
       <c r="H59" s="21">
-        <v>7.0868404607000004E-3</v>
+        <v>5.9171670631000001E-3</v>
       </c>
       <c r="I59" s="20">
-        <v>9.3800000000000008</v>
+        <v>7.95</v>
       </c>
       <c r="J59" s="15" t="s">
         <v>13</v>
@@ -3003,28 +3006,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="16" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D60" s="18">
-        <v>7.05</v>
+        <v>9.25</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="F60" s="19">
-        <v>411</v>
+        <v>3500</v>
       </c>
       <c r="G60" s="20">
-        <v>3941.67</v>
+        <v>3516</v>
       </c>
       <c r="H60" s="21">
-        <v>6.3416718554000001E-3</v>
+        <v>5.7306440525E-3</v>
       </c>
       <c r="I60" s="20">
-        <v>8.11</v>
+        <v>8.4</v>
       </c>
       <c r="J60" s="15" t="s">
         <v>13</v>
@@ -3032,28 +3035,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D61" s="18">
         <v>9.25</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F61" s="19">
         <v>3500</v>
       </c>
       <c r="G61" s="20">
-        <v>3490.4</v>
+        <v>3508.81</v>
       </c>
       <c r="H61" s="21">
-        <v>5.6156328266999999E-3</v>
+        <v>5.7189252439999996E-3</v>
       </c>
       <c r="I61" s="20">
-        <v>9.91</v>
+        <v>8</v>
       </c>
       <c r="J61" s="15" t="s">
         <v>13</v>
@@ -3061,28 +3064,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D62" s="18">
-        <v>9.25</v>
+        <v>9.58</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F62" s="19">
-        <v>3500</v>
+        <v>310</v>
       </c>
       <c r="G62" s="20">
-        <v>3480.27</v>
+        <v>3277.5</v>
       </c>
       <c r="H62" s="21">
-        <v>5.5993348779000002E-3</v>
+        <v>5.3419186240000003E-3</v>
       </c>
       <c r="I62" s="20">
-        <v>9.8000000000000007</v>
+        <v>8.83</v>
       </c>
       <c r="J62" s="15" t="s">
         <v>13</v>
@@ -3090,28 +3093,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D63" s="18">
-        <v>9.5399999999999991</v>
+        <v>10.1</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F63" s="19">
-        <v>310</v>
+        <v>3000</v>
       </c>
       <c r="G63" s="20">
-        <v>3261.85</v>
+        <v>3015.65</v>
       </c>
       <c r="H63" s="21">
-        <v>5.2479234287999997E-3</v>
+        <v>4.9151355907000004E-3</v>
       </c>
       <c r="I63" s="20">
-        <v>9.4499999999999993</v>
+        <v>9.76</v>
       </c>
       <c r="J63" s="15" t="s">
         <v>13</v>
@@ -3119,28 +3122,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D64" s="18">
-        <v>7.25</v>
+        <v>10</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="F64" s="19">
-        <v>300</v>
+        <v>2750</v>
       </c>
       <c r="G64" s="20">
-        <v>2987.88</v>
+        <v>2754.13</v>
       </c>
       <c r="H64" s="21">
-        <v>4.8071387263E-3</v>
+        <v>4.4888904165E-3</v>
       </c>
       <c r="I64" s="20">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="J64" s="15" t="s">
         <v>13</v>
@@ -3148,28 +3151,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="16" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D65" s="18">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="F65" s="19">
-        <v>3000</v>
+        <v>2750</v>
       </c>
       <c r="G65" s="20">
-        <v>2982.29</v>
+        <v>2753.68</v>
       </c>
       <c r="H65" s="21">
-        <v>4.7981450901999996E-3</v>
+        <v>4.4881569723000002E-3</v>
       </c>
       <c r="I65" s="20">
-        <v>10.44</v>
+        <v>9.35</v>
       </c>
       <c r="J65" s="15" t="s">
         <v>13</v>
@@ -3177,28 +3180,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="16" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D66" s="18">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="F66" s="19">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="G66" s="20">
-        <v>2745.78</v>
+        <v>2523.89</v>
       </c>
       <c r="H66" s="21">
-        <v>4.4176290118000004E-3</v>
+        <v>4.1136277637999997E-3</v>
       </c>
       <c r="I66" s="20">
-        <v>10.43</v>
+        <v>7.93</v>
       </c>
       <c r="J66" s="15" t="s">
         <v>13</v>
@@ -3206,28 +3209,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D67" s="18">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F67" s="19">
-        <v>2750</v>
+        <v>25</v>
       </c>
       <c r="G67" s="20">
-        <v>2744.95</v>
+        <v>2505.6799999999998</v>
       </c>
       <c r="H67" s="21">
-        <v>4.4162936419000001E-3</v>
+        <v>4.0839477217000002E-3</v>
       </c>
       <c r="I67" s="20">
-        <v>10.43</v>
+        <v>9.93</v>
       </c>
       <c r="J67" s="15" t="s">
         <v>13</v>
@@ -3235,57 +3238,57 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="16" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D68" s="18">
-        <v>9.9500000000000011</v>
+        <v>5.83</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F68" s="19">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="G68" s="20">
-        <v>2505.2600000000002</v>
+        <v>2487.5100000000002</v>
       </c>
       <c r="H68" s="21">
-        <v>4.0306613268999997E-3</v>
+        <v>4.0543328746E-3</v>
       </c>
       <c r="I68" s="20">
-        <v>9.5</v>
-      </c>
-      <c r="J68" s="15" t="s">
-        <v>13</v>
+        <v>5.93</v>
+      </c>
+      <c r="J68" s="15">
+        <v>6.88</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="16" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D69" s="18">
-        <v>8.35</v>
+        <v>9.58</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F69" s="19">
-        <v>2500</v>
+        <v>205</v>
       </c>
       <c r="G69" s="20">
-        <v>2503.79</v>
+        <v>2168.2399999999998</v>
       </c>
       <c r="H69" s="21">
-        <v>4.0282962741000003E-3</v>
+        <v>3.5339623607000001E-3</v>
       </c>
       <c r="I69" s="20">
-        <v>8.19</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="J69" s="15" t="s">
         <v>13</v>
@@ -3293,28 +3296,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="16" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D70" s="18">
-        <v>9.99</v>
+        <v>9.58</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="F70" s="19">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="G70" s="20">
-        <v>2493.2199999999998</v>
+        <v>2165.1799999999998</v>
       </c>
       <c r="H70" s="21">
-        <v>4.0112904183000004E-3</v>
+        <v>3.5289749400999998E-3</v>
       </c>
       <c r="I70" s="20">
-        <v>10.87</v>
+        <v>8.81</v>
       </c>
       <c r="J70" s="15" t="s">
         <v>13</v>
@@ -3322,28 +3325,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="16" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D71" s="18">
-        <v>9.99</v>
+        <v>9.58</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="F71" s="19">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="G71" s="20">
-        <v>2482.15</v>
+        <v>2157.14</v>
       </c>
       <c r="H71" s="21">
-        <v>3.9934801228E-3</v>
+        <v>3.515870737E-3</v>
       </c>
       <c r="I71" s="20">
-        <v>10.86</v>
+        <v>8.25</v>
       </c>
       <c r="J71" s="15" t="s">
         <v>13</v>
@@ -3351,42 +3354,42 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="16" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D72" s="18">
-        <v>5.83</v>
+        <v>9.58</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>74</v>
       </c>
       <c r="F72" s="19">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="G72" s="20">
-        <v>2454.25</v>
+        <v>2156.63</v>
       </c>
       <c r="H72" s="21">
-        <v>3.9485923861999998E-3</v>
+        <v>3.5150395003E-3</v>
       </c>
       <c r="I72" s="20">
-        <v>6.21</v>
-      </c>
-      <c r="J72" s="15">
-        <v>8.3699999999999992</v>
+        <v>7.06</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D73" s="18">
-        <v>9.5399999999999991</v>
+        <v>9.58</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>74</v>
@@ -3395,13 +3398,13 @@
         <v>205</v>
       </c>
       <c r="G73" s="20">
-        <v>2164.9499999999998</v>
+        <v>2156.46</v>
       </c>
       <c r="H73" s="21">
-        <v>3.4831435617999999E-3</v>
+        <v>3.5147624212999999E-3</v>
       </c>
       <c r="I73" s="20">
-        <v>9.2799999999999994</v>
+        <v>7.64</v>
       </c>
       <c r="J73" s="15" t="s">
         <v>13</v>
@@ -3409,13 +3412,13 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D74" s="18">
-        <v>9.5399999999999991</v>
+        <v>9.58</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>74</v>
@@ -3424,13 +3427,13 @@
         <v>205</v>
       </c>
       <c r="G74" s="20">
-        <v>2162.62</v>
+        <v>2156.2399999999998</v>
       </c>
       <c r="H74" s="21">
-        <v>3.4793948727000002E-3</v>
+        <v>3.5144038485999999E-3</v>
       </c>
       <c r="I74" s="20">
-        <v>9.36</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="J74" s="15" t="s">
         <v>13</v>
@@ -3438,13 +3441,13 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D75" s="18">
-        <v>9.5399999999999991</v>
+        <v>9.58</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>74</v>
@@ -3453,13 +3456,13 @@
         <v>205</v>
       </c>
       <c r="G75" s="20">
-        <v>2149.4299999999998</v>
+        <v>2153.92</v>
       </c>
       <c r="H75" s="21">
-        <v>3.4581737528E-3</v>
+        <v>3.5106225363000002E-3</v>
       </c>
       <c r="I75" s="20">
-        <v>9.3000000000000007</v>
+        <v>8.01</v>
       </c>
       <c r="J75" s="15" t="s">
         <v>13</v>
@@ -3467,28 +3470,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="16" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D76" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.85</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F76" s="19">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="G76" s="20">
-        <v>2140.7199999999998</v>
+        <v>2029.18</v>
       </c>
       <c r="H76" s="21">
-        <v>3.4441604127999998E-3</v>
+        <v>3.3073118027000001E-3</v>
       </c>
       <c r="I76" s="20">
-        <v>9.24</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="J76" s="15" t="s">
         <v>13</v>
@@ -3496,28 +3499,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="16" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D77" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F77" s="19">
-        <v>205</v>
+        <v>2000</v>
       </c>
       <c r="G77" s="20">
-        <v>2131.21</v>
+        <v>2026.17</v>
       </c>
       <c r="H77" s="21">
-        <v>3.4288599692E-3</v>
+        <v>3.3024058759000001E-3</v>
       </c>
       <c r="I77" s="20">
-        <v>9.18</v>
+        <v>7.34</v>
       </c>
       <c r="J77" s="15" t="s">
         <v>13</v>
@@ -3525,28 +3528,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="16" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D78" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F78" s="19">
-        <v>205</v>
+        <v>2000</v>
       </c>
       <c r="G78" s="20">
-        <v>2120.85</v>
+        <v>2016.92</v>
       </c>
       <c r="H78" s="21">
-        <v>3.4121919781E-3</v>
+        <v>3.2873295228000002E-3</v>
       </c>
       <c r="I78" s="20">
-        <v>9.1199999999999992</v>
+        <v>7.39</v>
       </c>
       <c r="J78" s="15" t="s">
         <v>13</v>
@@ -3554,28 +3557,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="16" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D79" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F79" s="19">
-        <v>205</v>
+        <v>2000</v>
       </c>
       <c r="G79" s="20">
-        <v>2109.56</v>
+        <v>2005.07</v>
       </c>
       <c r="H79" s="21">
-        <v>3.3940277291999998E-3</v>
+        <v>3.2680154921000001E-3</v>
       </c>
       <c r="I79" s="20">
-        <v>9.0399999999999991</v>
+        <v>7.3</v>
       </c>
       <c r="J79" s="15" t="s">
         <v>13</v>
@@ -3583,28 +3586,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="16" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D80" s="18">
-        <v>8.85</v>
+        <v>9.58</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="F80" s="19">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="G80" s="20">
-        <v>2012.32</v>
+        <v>1809.68</v>
       </c>
       <c r="H80" s="21">
-        <v>3.2375802916000001E-3</v>
+        <v>2.9495540183999999E-3</v>
       </c>
       <c r="I80" s="20">
-        <v>8.57</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="J80" s="15" t="s">
         <v>13</v>
@@ -3612,28 +3615,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="16" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D81" s="18">
-        <v>8.4499999999999993</v>
+        <v>9.58</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F81" s="19">
-        <v>2000</v>
+        <v>170</v>
       </c>
       <c r="G81" s="20">
-        <v>2003.81</v>
+        <v>1800.93</v>
       </c>
       <c r="H81" s="21">
-        <v>3.2238887275000002E-3</v>
+        <v>2.9352926034E-3</v>
       </c>
       <c r="I81" s="20">
-        <v>8.2799999999999994</v>
+        <v>8.93</v>
       </c>
       <c r="J81" s="15" t="s">
         <v>13</v>
@@ -3641,28 +3644,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="16" t="s">
-        <v>144</v>
+        <v>37</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D82" s="18">
-        <v>8.4499999999999993</v>
+        <v>8.65</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F82" s="19">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="G82" s="20">
-        <v>2002.86</v>
+        <v>1527.49</v>
       </c>
       <c r="H82" s="21">
-        <v>3.2223602920000002E-3</v>
+        <v>2.4896193071000002E-3</v>
       </c>
       <c r="I82" s="20">
-        <v>8.32</v>
+        <v>7.72</v>
       </c>
       <c r="J82" s="15" t="s">
         <v>13</v>
@@ -3670,28 +3673,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="16" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D83" s="18">
-        <v>8.4499999999999993</v>
+        <v>8.24</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F83" s="19">
-        <v>2000</v>
+        <v>130</v>
       </c>
       <c r="G83" s="20">
-        <v>1999.46</v>
+        <v>1302.31</v>
       </c>
       <c r="H83" s="21">
-        <v>3.2168901019000002E-3</v>
+        <v>2.1226038270999999E-3</v>
       </c>
       <c r="I83" s="20">
-        <v>8.3800000000000008</v>
+        <v>7.49</v>
       </c>
       <c r="J83" s="15" t="s">
         <v>13</v>
@@ -3699,28 +3702,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D84" s="18">
-        <v>8.4499999999999993</v>
+        <v>7.49</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F84" s="19">
-        <v>2000</v>
+        <v>9</v>
       </c>
       <c r="G84" s="20">
-        <v>1997.36</v>
+        <v>91.62</v>
       </c>
       <c r="H84" s="21">
-        <v>3.213511455E-3</v>
+        <v>1.4932924000000001E-4</v>
       </c>
       <c r="I84" s="20">
-        <v>8.43</v>
+        <v>6.5</v>
       </c>
       <c r="J84" s="15" t="s">
         <v>13</v>
@@ -3728,57 +3731,36 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="D85" s="18">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F85" s="19">
-        <v>170</v>
-      </c>
-      <c r="G85" s="20">
-        <v>1808.21</v>
-      </c>
-      <c r="H85" s="21">
-        <v>2.9091919074E-3</v>
-      </c>
-      <c r="I85" s="20">
-        <v>9.4700000000000006</v>
+        <v>13</v>
       </c>
       <c r="J85" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C86" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D86" s="18">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="E86" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F86" s="19">
-        <v>170</v>
-      </c>
-      <c r="G86" s="20">
-        <v>1806.2</v>
-      </c>
-      <c r="H86" s="21">
-        <v>2.9059580596999999E-3</v>
-      </c>
-      <c r="I86" s="20">
-        <v>9.43</v>
+      <c r="B86" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J86" s="15" t="s">
         <v>13</v>
@@ -3786,57 +3768,36 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="C87" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D87" s="18">
-        <v>8.24</v>
-      </c>
-      <c r="E87" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F87" s="19">
-        <v>130</v>
-      </c>
-      <c r="G87" s="20">
-        <v>1293.54</v>
-      </c>
-      <c r="H87" s="21">
-        <v>2.0811499217000002E-3</v>
-      </c>
-      <c r="I87" s="20">
-        <v>8.77</v>
+        <v>13</v>
       </c>
       <c r="J87" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D88" s="18">
-        <v>7.49</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F88" s="19">
-        <v>9</v>
-      </c>
-      <c r="G88" s="20">
-        <v>90.24</v>
-      </c>
-      <c r="H88" s="21">
-        <v>1.4518528139999999E-4</v>
-      </c>
-      <c r="I88" s="20">
-        <v>7.35</v>
+      <c r="B88" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="13">
+        <v>21162.02</v>
+      </c>
+      <c r="H88" s="14">
+        <v>3.4491468729499999E-2</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J88" s="15" t="s">
         <v>13</v>
@@ -3844,43 +3805,64 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="16" t="s">
-        <v>13</v>
+        <v>157</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D89" s="18">
+        <v>9.9</v>
+      </c>
+      <c r="E89" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F89" s="19">
+        <v>2100</v>
+      </c>
+      <c r="G89" s="20">
+        <v>21162.02</v>
+      </c>
+      <c r="H89" s="21">
+        <v>3.4491468729499999E-2</v>
+      </c>
+      <c r="I89" s="20">
+        <v>9.36</v>
       </c>
       <c r="J89" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H90" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="I90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="16" t="s">
+      <c r="H91" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I91" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J91" s="15" t="s">
@@ -3888,28 +3870,7 @@
       </c>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="13">
-        <v>21020.94</v>
-      </c>
-      <c r="H92" s="14">
-        <v>3.3820158352299998E-2</v>
-      </c>
-      <c r="I92" s="13" t="s">
+      <c r="B92" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J92" s="15" t="s">
@@ -3917,29 +3878,29 @@
       </c>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="C93" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D93" s="18">
-        <v>9.9</v>
-      </c>
-      <c r="E93" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F93" s="19">
-        <v>2100</v>
-      </c>
-      <c r="G93" s="20">
-        <v>21020.94</v>
-      </c>
-      <c r="H93" s="21">
-        <v>3.3820158352299998E-2</v>
-      </c>
-      <c r="I93" s="20">
-        <v>10.27</v>
+      <c r="B93" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J93" s="15" t="s">
         <v>13</v>
@@ -3955,7 +3916,7 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>13</v>
@@ -3970,10 +3931,10 @@
         <v>13</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H95" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>13</v>
@@ -3992,7 +3953,7 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>13</v>
@@ -4007,10 +3968,10 @@
         <v>13</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H97" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>13</v>
@@ -4029,7 +3990,7 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>13</v>
@@ -4043,11 +4004,11 @@
       <c r="F99" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G99" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H99" s="14" t="s">
-        <v>156</v>
+      <c r="G99" s="13">
+        <v>21254.63</v>
+      </c>
+      <c r="H99" s="14">
+        <v>3.4642411546599999E-2</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>13</v>
@@ -4066,7 +4027,7 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>13</v>
@@ -4080,11 +4041,11 @@
       <c r="F101" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G101" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H101" s="14" t="s">
-        <v>156</v>
+      <c r="G101" s="13">
+        <v>21254.63</v>
+      </c>
+      <c r="H101" s="14">
+        <v>3.4642411546599999E-2</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>13</v>
@@ -4095,36 +4056,57 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="16" t="s">
-        <v>13</v>
+        <v>165</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="F102" s="19">
+        <v>2000</v>
+      </c>
+      <c r="G102" s="20">
+        <v>9398.0300000000007</v>
+      </c>
+      <c r="H102" s="21">
+        <v>1.5317623641900001E-2</v>
+      </c>
+      <c r="I102" s="20">
+        <v>6.48</v>
       </c>
       <c r="J102" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C103" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="13">
-        <v>34825.89</v>
-      </c>
-      <c r="H103" s="14">
-        <v>5.6030658693499998E-2</v>
-      </c>
-      <c r="I103" s="13" t="s">
-        <v>13</v>
+      <c r="B103" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D103" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G103" s="20">
+        <v>4772.6899999999996</v>
+      </c>
+      <c r="H103" s="21">
+        <v>7.7788929359999997E-3</v>
+      </c>
+      <c r="I103" s="20">
+        <v>6.41</v>
       </c>
       <c r="J103" s="15" t="s">
         <v>13</v>
@@ -4132,36 +4114,57 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="16" t="s">
-        <v>13</v>
+        <v>170</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="F104" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G104" s="20">
+        <v>4703</v>
+      </c>
+      <c r="H104" s="21">
+        <v>7.6653068768E-3</v>
+      </c>
+      <c r="I104" s="20">
+        <v>6.53</v>
       </c>
       <c r="J104" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="13">
-        <v>34825.89</v>
-      </c>
-      <c r="H105" s="14">
-        <v>5.6030658693499998E-2</v>
-      </c>
-      <c r="I105" s="13" t="s">
-        <v>13</v>
+      <c r="B105" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D105" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="F105" s="19">
+        <v>500</v>
+      </c>
+      <c r="G105" s="20">
+        <v>2380.91</v>
+      </c>
+      <c r="H105" s="21">
+        <v>3.8805880919000001E-3</v>
+      </c>
+      <c r="I105" s="20">
+        <v>6.81</v>
       </c>
       <c r="J105" s="15" t="s">
         <v>13</v>
@@ -4169,57 +4172,36 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="C106" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="D106" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F106" s="19">
-        <v>3200</v>
-      </c>
-      <c r="G106" s="20">
-        <v>15914.3</v>
-      </c>
-      <c r="H106" s="21">
-        <v>2.5604190205900001E-2</v>
-      </c>
-      <c r="I106" s="20">
-        <v>7.28</v>
+        <v>13</v>
       </c>
       <c r="J106" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="C107" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D107" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F107" s="19">
-        <v>1000</v>
-      </c>
-      <c r="G107" s="20">
-        <v>4998.17</v>
-      </c>
-      <c r="H107" s="21">
-        <v>8.0414529925999997E-3</v>
-      </c>
-      <c r="I107" s="20">
-        <v>6.69</v>
+      <c r="B107" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I107" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J107" s="15" t="s">
         <v>13</v>
@@ -4227,57 +4209,36 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C108" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D108" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F108" s="19">
-        <v>1000</v>
-      </c>
-      <c r="G108" s="20">
-        <v>4974.1400000000003</v>
-      </c>
-      <c r="H108" s="21">
-        <v>8.0027916195000003E-3</v>
-      </c>
-      <c r="I108" s="20">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="J108" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C109" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="D109" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F109" s="19">
-        <v>1000</v>
-      </c>
-      <c r="G109" s="20">
-        <v>4962.29</v>
-      </c>
-      <c r="H109" s="21">
-        <v>7.9837263979999993E-3</v>
-      </c>
-      <c r="I109" s="20">
-        <v>7.3</v>
+      <c r="B109" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H109" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I109" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J109" s="15" t="s">
         <v>13</v>
@@ -4285,57 +4246,36 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="C110" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="D110" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F110" s="19">
-        <v>400</v>
-      </c>
-      <c r="G110" s="20">
-        <v>1992.43</v>
-      </c>
-      <c r="H110" s="21">
-        <v>3.2055796793999999E-3</v>
-      </c>
-      <c r="I110" s="20">
-        <v>7.3</v>
-      </c>
-      <c r="J110" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="C111" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="D111" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F111" s="19">
-        <v>400</v>
-      </c>
-      <c r="G111" s="20">
-        <v>1984.56</v>
-      </c>
-      <c r="H111" s="21">
-        <v>3.1929177981000001E-3</v>
-      </c>
-      <c r="I111" s="20">
-        <v>7.28</v>
+      <c r="C111" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H111" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I111" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J111" s="15" t="s">
         <v>13</v>
@@ -4351,7 +4291,7 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>13</v>
@@ -4365,11 +4305,11 @@
       <c r="F113" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G113" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H113" s="14" t="s">
-        <v>156</v>
+      <c r="G113" s="13">
+        <v>9909.5099999999984</v>
+      </c>
+      <c r="H113" s="14">
+        <v>1.6151272623599999E-2</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>13</v>
@@ -4380,6 +4320,27 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D114" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F114" s="19">
+        <v>5000250</v>
+      </c>
+      <c r="G114" s="20">
+        <v>5593.78</v>
+      </c>
+      <c r="H114" s="21">
+        <v>9.1171678294000007E-3</v>
+      </c>
+      <c r="I114" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J114" s="15" t="s">
@@ -4387,28 +4348,28 @@
       </c>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H115" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="I115" s="13" t="s">
+      <c r="B115" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C115" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D115" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F115" s="19">
+        <v>1975000</v>
+      </c>
+      <c r="G115" s="20">
+        <v>2923</v>
+      </c>
+      <c r="H115" s="21">
+        <v>4.7641275782999998E-3</v>
+      </c>
+      <c r="I115" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J115" s="15" t="s">
@@ -4417,6 +4378,27 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D116" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F116" s="19">
+        <v>1515150</v>
+      </c>
+      <c r="G116" s="20">
+        <v>1392.73</v>
+      </c>
+      <c r="H116" s="21">
+        <v>2.2699772159E-3</v>
+      </c>
+      <c r="I116" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J116" s="15" t="s">
@@ -4424,28 +4406,7 @@
       </c>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F117" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H117" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="I117" s="13" t="s">
+      <c r="B117" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J117" s="15" t="s">
@@ -4453,7 +4414,28 @@
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="16" t="s">
+      <c r="B118" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="13">
+        <v>41093.12000000001</v>
+      </c>
+      <c r="H118" s="14">
+        <v>6.69766904803E-2</v>
+      </c>
+      <c r="I118" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J118" s="15" t="s">
@@ -4461,28 +4443,28 @@
       </c>
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G119" s="13">
-        <v>10036.349999999999</v>
-      </c>
-      <c r="H119" s="14">
-        <v>1.6147277252100002E-2</v>
-      </c>
-      <c r="I119" s="13" t="s">
+      <c r="B119" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D119" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="F119" s="19">
+        <v>6779406</v>
+      </c>
+      <c r="G119" s="20">
+        <v>25856.65</v>
+      </c>
+      <c r="H119" s="21">
+        <v>4.2143133544199997E-2</v>
+      </c>
+      <c r="I119" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J119" s="15" t="s">
@@ -4491,25 +4473,25 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="16" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D120" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F120" s="19">
-        <v>5000250</v>
+        <v>2008739</v>
       </c>
       <c r="G120" s="20">
-        <v>5662.78</v>
+        <v>7934.12</v>
       </c>
       <c r="H120" s="21">
-        <v>9.1107303628999992E-3</v>
+        <v>1.29316318516E-2</v>
       </c>
       <c r="I120" s="20" t="s">
         <v>13</v>
@@ -4520,25 +4502,25 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="D121" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C121" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D121" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E121" s="17" t="s">
-        <v>184</v>
-      </c>
       <c r="F121" s="19">
-        <v>2200000</v>
+        <v>2285584</v>
       </c>
       <c r="G121" s="20">
-        <v>2871</v>
+        <v>6992.52</v>
       </c>
       <c r="H121" s="21">
-        <v>4.6190928964000002E-3</v>
+        <v>1.13969406002E-2</v>
       </c>
       <c r="I121" s="20" t="s">
         <v>13</v>
@@ -4549,25 +4531,25 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="16" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C122" s="17" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D122" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F122" s="19">
-        <v>1515150</v>
+        <v>229672</v>
       </c>
       <c r="G122" s="20">
-        <v>1502.57</v>
+        <v>309.83</v>
       </c>
       <c r="H122" s="21">
-        <v>2.4174539928000002E-3</v>
+        <v>5.0498448430000005E-4</v>
       </c>
       <c r="I122" s="20" t="s">
         <v>13</v>
@@ -4586,7 +4568,7 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="11" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>13</v>
@@ -4601,10 +4583,10 @@
         <v>13</v>
       </c>
       <c r="G124" s="13">
-        <v>40115.72</v>
+        <v>2200.1799999999998</v>
       </c>
       <c r="H124" s="14">
-        <v>6.4541357466299992E-2</v>
+        <v>3.5860206005000001E-3</v>
       </c>
       <c r="I124" s="13" t="s">
         <v>13</v>
@@ -4615,25 +4597,25 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="16" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D125" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F125" s="19">
-        <v>6954163</v>
+        <v>19660.316999999999</v>
       </c>
       <c r="G125" s="20">
-        <v>25740.14</v>
+        <v>2200.1799999999998</v>
       </c>
       <c r="H125" s="21">
-        <v>4.1412782245299998E-2</v>
+        <v>3.5860206005000001E-3</v>
       </c>
       <c r="I125" s="20" t="s">
         <v>13</v>
@@ -4644,27 +4626,6 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C126" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D126" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="F126" s="19">
-        <v>2021810</v>
-      </c>
-      <c r="G126" s="20">
-        <v>7561.57</v>
-      </c>
-      <c r="H126" s="21">
-        <v>1.2165654570700001E-2</v>
-      </c>
-      <c r="I126" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J126" s="15" t="s">
@@ -4672,28 +4633,28 @@
       </c>
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="C127" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D127" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="F127" s="19">
-        <v>2285584</v>
-      </c>
-      <c r="G127" s="20">
-        <v>6814.01</v>
-      </c>
-      <c r="H127" s="21">
-        <v>1.0962920650300001E-2</v>
-      </c>
-      <c r="I127" s="20" t="s">
+      <c r="B127" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="13">
+        <v>13574.53</v>
+      </c>
+      <c r="H127" s="14">
+        <v>2.2124800799400001E-2</v>
+      </c>
+      <c r="I127" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J127" s="15" t="s">
@@ -4709,102 +4670,144 @@
       </c>
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="13">
-        <v>2145.06</v>
-      </c>
-      <c r="H129" s="14">
-        <v>3.4511429496000001E-3</v>
-      </c>
-      <c r="I129" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J129" s="15" t="s">
+      <c r="B129" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="C129" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="23">
+        <v>13286.38308440987</v>
+      </c>
+      <c r="H129" s="24">
+        <v>2.1655157054228075E-2</v>
+      </c>
+      <c r="I129" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C130" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="D130" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E130" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="F130" s="19">
-        <v>19660.316999999999</v>
-      </c>
-      <c r="G130" s="20">
-        <v>2145.06</v>
-      </c>
-      <c r="H130" s="21">
-        <v>3.4511429496000001E-3</v>
-      </c>
-      <c r="I130" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J130" s="15" t="s">
+      <c r="B130" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="C130" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="23">
+        <v>613543.60308440996</v>
+      </c>
+      <c r="H130" s="24">
+        <v>0.99999999999572797</v>
+      </c>
+      <c r="I130" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J131" s="15" t="s">
+      <c r="B131" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D132" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E132" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F132" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G132" s="13">
-        <v>9843.39</v>
-      </c>
-      <c r="H132" s="14">
-        <v>1.5836827873699999E-2</v>
-      </c>
-      <c r="I132" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J132" s="15" t="s">
+      <c r="B132" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C132" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="23">
+        <v>-5000</v>
+      </c>
+      <c r="H132" s="24">
+        <v>-8.1493800519864788E-3</v>
+      </c>
+      <c r="I132" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J132" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="20">
+        <v>10000</v>
+      </c>
+      <c r="H133" s="21">
+        <v>1.6298760103972958E-2</v>
+      </c>
+      <c r="I133" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J133" s="15" t="s">
@@ -4812,300 +4815,266 @@
       </c>
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C134" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D134" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G134" s="23">
-        <v>17945.478396649938</v>
-      </c>
-      <c r="H134" s="24">
-        <v>2.8872111384368265E-2</v>
-      </c>
-      <c r="I134" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J134" s="25" t="s">
+      <c r="B134" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H134" s="21">
+        <v>-8.1493800519864788E-3</v>
+      </c>
+      <c r="I134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J134" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="C135" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D135" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G135" s="23">
-        <v>621550.60839664994</v>
-      </c>
-      <c r="H135" s="24">
-        <v>0.99999999999536815</v>
-      </c>
-      <c r="I135" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J135" s="25" t="s">
+      <c r="B135" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="20">
+        <v>-2500</v>
+      </c>
+      <c r="H135" s="21">
+        <v>-4.0746900259932394E-3</v>
+      </c>
+      <c r="I135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J135" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C136" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D136" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E136" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F136" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G136" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H136" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="I136" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J136" s="25" t="s">
+      <c r="B136" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" s="20">
+        <v>-2500</v>
+      </c>
+      <c r="H136" s="21">
+        <v>-4.0746900259932394E-3</v>
+      </c>
+      <c r="I136" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J136" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="C137" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D137" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F137" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G137" s="23">
-        <v>10000</v>
-      </c>
-      <c r="H137" s="24">
-        <v>1.6088794484162713E-2</v>
-      </c>
-      <c r="I137" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J137" s="25" t="s">
+      <c r="B137" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H137" s="21">
+        <v>-8.1493800519864788E-3</v>
+      </c>
+      <c r="I137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J137" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G138" s="20">
-        <v>10000</v>
-      </c>
-      <c r="H138" s="21">
-        <v>1.6088794484162713E-2</v>
-      </c>
-      <c r="I138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J138" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I139" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="J139" s="26" t="s">
-        <v>13</v>
-      </c>
+      <c r="B138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I138" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J138" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C142" s="5"/>
-      <c r="D142" s="5"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="5"/>
-      <c r="G142" s="5"/>
-      <c r="H142" s="5"/>
-      <c r="I142" s="5"/>
+      <c r="B142" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C143" s="5"/>
-      <c r="D143" s="5"/>
-      <c r="E143" s="5"/>
-      <c r="F143" s="5"/>
-      <c r="G143" s="5"/>
-      <c r="H143" s="5"/>
+      <c r="B143" s="17" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="17" t="s">
-        <v>217</v>
-      </c>
+      <c r="B144" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
     </row>
     <row r="145" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C145" s="5"/>
-      <c r="D145" s="5"/>
-      <c r="E145" s="5"/>
-      <c r="F145" s="5"/>
-      <c r="G145" s="5"/>
-      <c r="H145" s="5"/>
-    </row>
-    <row r="146" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C146" s="5"/>
-      <c r="D146" s="5"/>
-      <c r="E146" s="5"/>
-      <c r="F146" s="5"/>
-      <c r="G146" s="5"/>
-      <c r="H146" s="5"/>
+      <c r="B145" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+    </row>
+    <row r="146" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
     </row>
     <row r="147" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C147" s="5"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
-      <c r="G147" s="5"/>
-      <c r="H147" s="5"/>
+      <c r="B147" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
     </row>
     <row r="148" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C148" s="5"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
-      <c r="H148" s="5"/>
-    </row>
-    <row r="149" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C149" s="5"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
-      <c r="H149" s="5"/>
-    </row>
-    <row r="150" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-    </row>
-    <row r="153" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B153" s="27" t="s">
+      <c r="B148" s="1" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="168" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B168" s="27" t="s">
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="2:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="169" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B169" s="27" t="s">
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+    </row>
+    <row r="152" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B152" s="27" t="s">
         <v>215</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B167" s="27" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B142:I142"/>
-    <mergeCell ref="B143:H143"/>
-    <mergeCell ref="B150:G150"/>
+    <mergeCell ref="B149:G149"/>
+    <mergeCell ref="B144:H144"/>
     <mergeCell ref="B145:H145"/>
     <mergeCell ref="B146:H146"/>
     <mergeCell ref="B147:H147"/>
     <mergeCell ref="B148:H148"/>
-    <mergeCell ref="B149:H149"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B141:I141"/>
+    <mergeCell ref="B142:H142"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
